--- a/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-MOPEDClaimResponse.xlsx
+++ b/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-MOPEDClaimResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:50:17+00:00</t>
+    <t>2024-10-29T09:11:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -599,7 +599,7 @@
     <t>rechnungsnummerKHLGF</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-rechnungsnummerKhlgf}
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-rechnungsnummerKHLGF}
 </t>
   </si>
   <si>
@@ -660,13 +660,13 @@
     <t>MOPED Extension für die Anzahl der Sonderleistungen</t>
   </si>
   <si>
-    <t>ClaimResponse.extension:punkteLdfPauschale</t>
-  </si>
-  <si>
-    <t>punkteLdfPauschale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-PunkteLdfPauschale}
+    <t>ClaimResponse.extension:punkteLDFPauschale</t>
+  </si>
+  <si>
+    <t>punkteLDFPauschale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-punkteLDFPauschale}
 </t>
   </si>
   <si>
@@ -676,13 +676,13 @@
     <t>MOPED Extension für die LDF Punkte Pauschale</t>
   </si>
   <si>
-    <t>ClaimResponse.extension:konstenmeldungArk</t>
-  </si>
-  <si>
-    <t>konstenmeldungArk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-konstenmeldungArk}
+    <t>ClaimResponse.extension:konstenmeldungARK</t>
+  </si>
+  <si>
+    <t>konstenmeldungARK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-konstenmeldungARK}
 </t>
   </si>
   <si>
